--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -62863,6 +62863,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -62932,6 +62932,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>1.07000005245209</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>6800</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>1.0900000333786</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -62796,7 +62796,7 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
         <v>0</v>
@@ -62819,7 +62819,7 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
         <v>0</v>
@@ -62842,7 +62842,7 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
         <v>0</v>
@@ -62865,7 +62865,7 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
         <v>0</v>
@@ -62888,7 +62888,7 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
         <v>0</v>
@@ -62911,7 +62911,7 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
         <v>0</v>
@@ -62934,7 +62934,7 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
         <v>0</v>
@@ -62957,22 +62957,22 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="C2722" t="n">
-        <v>1.0900000333786</v>
+        <v>1.07000005245209</v>
       </c>
       <c r="D2722" t="n">
-        <v>1.0900000333786</v>
+        <v>1.07000005245209</v>
       </c>
       <c r="E2722" t="n">
-        <v>1.0900000333786</v>
+        <v>1.07000005245209</v>
       </c>
       <c r="F2722" t="n">
-        <v>1.0900000333786</v>
+        <v>1.07000005245209</v>
       </c>
       <c r="G2722" t="s">
         <v>7</v>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63070,6 +63070,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2727" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63093,6 +63093,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2728" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63116,6 +63116,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2729" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63139,6 +63139,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2730" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63270,7 +63270,9 @@
       <c r="E2735" t="n">
         <v>1.02999997138977</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>1.02999997138977</v>
+      </c>
       <c r="G2735" t="s">
         <v>7</v>
       </c>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63277,6 +63277,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="F2736" t="n">
+        <v>1.02999997138977</v>
+      </c>
+      <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>1600</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>1.01999998092651</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>1.01999998092651</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>1.01999998092651</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63339,7 +63339,9 @@
       <c r="E2738" t="n">
         <v>1.01999998092651</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>1.03999996185303</v>
+      </c>
       <c r="G2738" t="s">
         <v>7</v>
       </c>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>1.03999996185303</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/LMG.MI.xlsx
+++ b/data/LMG.MI.xlsx
@@ -63438,6 +63438,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>1.05999994277954</v>
+      </c>
+      <c r="G2743" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
